--- a/pensum/ol20/OL20_Noen_viktige_lover_Regneark_Arbeidstid_og_overtid.xlsx
+++ b/pensum/ol20/OL20_Noen_viktige_lover_Regneark_Arbeidstid_og_overtid.xlsx
@@ -1217,7 +1217,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1384,6 +1384,10 @@
     </xf>
     <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1674,7 +1678,7 @@
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="24.75" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1696,7 +1700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -1718,7 +1722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="24.75" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>11</v>
       </c>
@@ -1797,7 +1801,7 @@
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="32.25" customHeight="true" r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
         <v>24</v>
       </c>
@@ -2214,8 +2218,8 @@
         <v>91</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="20" t="s">
+    <row ht="27" customHeight="true" r="53" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A53" t="s">
         <v>97</v>
       </c>
       <c r="B53" s="22" t="s">
@@ -2311,8 +2315,8 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+    <row ht="27" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A5" t="s">
         <v>111</v>
       </c>
       <c r="B5" s="24" t="n">
@@ -2322,8 +2326,8 @@
         <v>112</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A6" t="s">
         <v>113</v>
       </c>
       <c r="B6" s="25" t="n">
@@ -2331,8 +2335,8 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row ht="39.75" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A7" t="s">
         <v>114</v>
       </c>
       <c r="B7" s="24" t="n">
@@ -2342,8 +2346,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+    <row ht="39.75" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A8" t="s">
         <v>116</v>
       </c>
       <c r="B8" s="24" t="n">
@@ -2353,8 +2357,8 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A9" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="24" t="n">
@@ -2364,8 +2368,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+    <row ht="39.75" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A10" t="s">
         <v>120</v>
       </c>
       <c r="B10" s="24" t="n">
@@ -2375,8 +2379,8 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row ht="27" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A11" t="s">
         <v>122</v>
       </c>
       <c r="B11" s="24" t="n">
@@ -2386,8 +2390,8 @@
         <v>123</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row ht="27" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A12" t="s">
         <v>124</v>
       </c>
       <c r="B12" s="24" t="n">
@@ -3331,8 +3335,8 @@
         <v>704640</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="s">
+    <row ht="27" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A19" t="s">
         <v>222</v>
       </c>
       <c r="B19" s="31" t="n">
@@ -3836,8 +3840,8 @@
         <v>278</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A6" t="s">
         <v>279</v>
       </c>
       <c r="B6" s="32" t="n">
@@ -4358,16 +4362,16 @@
         <v>110</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+    <row ht="27" customHeight="true" r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A5" t="s">
         <v>111</v>
       </c>
       <c r="B5" s="24" t="n">
         <v>37.5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A6" t="s">
         <v>113</v>
       </c>
       <c r="B6" s="25" t="n">
@@ -4375,48 +4379,48 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row ht="39.75" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A7" t="s">
         <v>114</v>
       </c>
       <c r="B7" s="24" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+    <row ht="39.75" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A8" t="s">
         <v>116</v>
       </c>
       <c r="B8" s="24" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+    <row ht="27" customHeight="true" r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A9" t="s">
         <v>118</v>
       </c>
       <c r="B9" s="24" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+    <row ht="39.75" customHeight="true" r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A10" t="s">
         <v>120</v>
       </c>
       <c r="B10" s="24" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row ht="27" customHeight="true" r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A11" t="s">
         <v>122</v>
       </c>
       <c r="B11" s="24" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row ht="27" customHeight="true" r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="42" r="A12" t="s">
         <v>124</v>
       </c>
       <c r="B12" s="24" t="n">
